--- a/Mentor-III-CSE-C.xlsx
+++ b/Mentor-III-CSE-C.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Downloads\Fw_ Mentor Mentee Allocation- 2026-2027 ODD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FREE LANCING\od system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964891D6-3AC0-4271-8AC2-B06B0A633E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222C077E-44DD-4882-9072-CBB80CC2DFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="III CSE C" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="170">
   <si>
     <t>REGISTER NUMBER</t>
   </si>
@@ -529,6 +529,15 @@
   </si>
   <si>
     <t>DR.A.ANANDH</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -955,7 +964,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H67"/>
+  <dimension ref="A2:I67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
@@ -965,9 +974,10 @@
     <col min="6" max="6" width="58.6640625" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" customWidth="1"/>
     <col min="8" max="8" width="25.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -992,8 +1002,11 @@
       <c r="H2" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I2" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1018,8 +1031,11 @@
       <c r="H3" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1044,8 +1060,11 @@
       <c r="H4" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1070,8 +1089,11 @@
       <c r="H5" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1096,8 +1118,11 @@
       <c r="H6" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1122,8 +1147,11 @@
       <c r="H7" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1148,8 +1176,11 @@
       <c r="H8" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1174,8 +1205,11 @@
       <c r="H9" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -1200,8 +1234,11 @@
       <c r="H10" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1226,8 +1263,11 @@
       <c r="H11" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -1252,8 +1292,11 @@
       <c r="H12" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -1278,8 +1321,11 @@
       <c r="H13" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -1304,8 +1350,11 @@
       <c r="H14" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -1330,8 +1379,11 @@
       <c r="H15" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -1356,8 +1408,11 @@
       <c r="H16" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -1382,8 +1437,11 @@
       <c r="H17" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -1408,8 +1466,11 @@
       <c r="H18" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -1434,8 +1495,11 @@
       <c r="H19" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -1460,8 +1524,11 @@
       <c r="H20" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I20" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -1486,8 +1553,11 @@
       <c r="H21" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -1512,8 +1582,11 @@
       <c r="H22" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -1538,8 +1611,11 @@
       <c r="H23" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -1564,8 +1640,11 @@
       <c r="H24" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -1590,8 +1669,11 @@
       <c r="H25" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -1616,8 +1698,11 @@
       <c r="H26" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -1642,8 +1727,11 @@
       <c r="H27" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -1668,8 +1756,11 @@
       <c r="H28" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -1694,8 +1785,11 @@
       <c r="H29" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -1720,8 +1814,11 @@
       <c r="H30" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -1746,8 +1843,11 @@
       <c r="H31" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -1772,8 +1872,11 @@
       <c r="H32" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -1798,8 +1901,11 @@
       <c r="H33" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -1824,8 +1930,11 @@
       <c r="H34" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I34" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -1850,8 +1959,11 @@
       <c r="H35" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -1876,8 +1988,11 @@
       <c r="H36" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -1902,8 +2017,11 @@
       <c r="H37" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -1928,8 +2046,11 @@
       <c r="H38" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -1954,8 +2075,11 @@
       <c r="H39" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -1980,8 +2104,11 @@
       <c r="H40" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -2006,8 +2133,11 @@
       <c r="H41" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2032,8 +2162,11 @@
       <c r="H42" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>41</v>
       </c>
@@ -2058,8 +2191,11 @@
       <c r="H43" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>42</v>
       </c>
@@ -2084,8 +2220,11 @@
       <c r="H44" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>43</v>
       </c>
@@ -2110,8 +2249,11 @@
       <c r="H45" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I45" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>44</v>
       </c>
@@ -2136,8 +2278,11 @@
       <c r="H46" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I46" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>45</v>
       </c>
@@ -2162,8 +2307,11 @@
       <c r="H47" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2188,8 +2336,11 @@
       <c r="H48" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I48" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -2214,8 +2365,11 @@
       <c r="H49" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>48</v>
       </c>
@@ -2240,8 +2394,11 @@
       <c r="H50" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I50" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -2266,8 +2423,11 @@
       <c r="H51" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I51" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -2292,8 +2452,11 @@
       <c r="H52" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -2318,8 +2481,11 @@
       <c r="H53" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -2344,8 +2510,11 @@
       <c r="H54" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -2370,8 +2539,11 @@
       <c r="H55" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -2396,8 +2568,11 @@
       <c r="H56" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -2422,8 +2597,11 @@
       <c r="H57" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I57" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -2448,8 +2626,11 @@
       <c r="H58" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I58" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -2474,8 +2655,11 @@
       <c r="H59" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -2500,8 +2684,11 @@
       <c r="H60" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I60" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -2526,8 +2713,11 @@
       <c r="H61" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I61" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>60</v>
       </c>
@@ -2548,8 +2738,11 @@
       <c r="H62" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I62" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>61</v>
       </c>
@@ -2570,8 +2763,11 @@
       <c r="H63" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>62</v>
       </c>
@@ -2592,8 +2788,11 @@
       <c r="H64" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I64" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="11">
         <v>63</v>
       </c>
@@ -2614,8 +2813,11 @@
       <c r="H65" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>64</v>
       </c>
@@ -2636,8 +2838,11 @@
       <c r="H66" s="8" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="11">
         <v>65</v>
       </c>
@@ -2657,6 +2862,9 @@
       </c>
       <c r="H67" s="8" t="s">
         <v>123</v>
+      </c>
+      <c r="I67" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
